--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="2207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3202" uniqueCount="2213">
   <si>
     <t>Category</t>
   </si>
@@ -6858,6 +6858,24 @@
   </si>
   <si>
     <t xml:space="preserve"> - 被{0}炸死</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - burnt by {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 被{0}烧死</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Alive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   存活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Die  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   死亡</t>
   </si>
   <si>
     <t>Yikes, that Sheriff shot backfired.</t>
@@ -7149,13 +7167,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="MS Gothic"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -7967,7 +7985,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R1092"/>
+  <dimension ref="A1:R1095"/>
   <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="40.375" style="1" customWidth="1"/>
@@ -23083,67 +23101,67 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="897" spans="1:5">
-      <c r="A897" s="3"/>
-      <c r="B897" s="3"/>
-      <c r="C897" s="3"/>
+    <row r="897" spans="1:16">
+      <c r="A897" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B897" s="3">
+        <v>21</v>
+      </c>
+      <c r="C897" s="3" t="s">
+        <v>2181</v>
+      </c>
       <c r="D897" s="3"/>
       <c r="E897" s="3"/>
+      <c r="P897" s="1" t="s">
+        <v>2182</v>
+      </c>
     </row>
     <row r="898" spans="1:16">
       <c r="A898" s="3" t="s">
-        <v>1615</v>
+        <v>2142</v>
       </c>
       <c r="B898" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C898" s="3" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="D898" s="3"/>
       <c r="E898" s="3"/>
       <c r="P898" s="1" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="899" spans="1:16">
       <c r="A899" s="3" t="s">
-        <v>1615</v>
+        <v>2142</v>
       </c>
       <c r="B899" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C899" s="3" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="D899" s="3"/>
       <c r="E899" s="3"/>
       <c r="P899" s="1" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="900" spans="1:16">
-      <c r="A900" s="3" t="s">
-        <v>1615</v>
-      </c>
-      <c r="B900" s="3">
-        <v>7</v>
-      </c>
-      <c r="C900" s="3" t="s">
-        <v>2185</v>
-      </c>
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="900" spans="1:5">
+      <c r="A900" s="3"/>
+      <c r="B900" s="3"/>
+      <c r="C900" s="3"/>
       <c r="D900" s="3"/>
       <c r="E900" s="3"/>
-      <c r="P900" s="1" t="s">
-        <v>2186</v>
-      </c>
     </row>
     <row r="901" spans="1:16">
       <c r="A901" s="3" t="s">
         <v>1615</v>
       </c>
       <c r="B901" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C901" s="3" t="s">
         <v>2187</v>
@@ -23159,7 +23177,7 @@
         <v>1615</v>
       </c>
       <c r="B902" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C902" s="3" t="s">
         <v>2189</v>
@@ -23175,7 +23193,7 @@
         <v>1615</v>
       </c>
       <c r="B903" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C903" s="3" t="s">
         <v>2191</v>
@@ -23186,12 +23204,12 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="904" ht="31" spans="1:16">
+    <row r="904" spans="1:16">
       <c r="A904" s="3" t="s">
         <v>1615</v>
       </c>
       <c r="B904" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C904" s="3" t="s">
         <v>2193</v>
@@ -23207,7 +23225,7 @@
         <v>1615</v>
       </c>
       <c r="B905" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C905" s="3" t="s">
         <v>2195</v>
@@ -23223,23 +23241,23 @@
         <v>1615</v>
       </c>
       <c r="B906" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C906" s="3" t="s">
         <v>2197</v>
       </c>
       <c r="D906" s="3"/>
       <c r="E906" s="3"/>
-      <c r="P906" s="15" t="s">
+      <c r="P906" s="1" t="s">
         <v>2198</v>
       </c>
     </row>
-    <row r="907" spans="1:16">
+    <row r="907" ht="31" spans="1:16">
       <c r="A907" s="3" t="s">
         <v>1615</v>
       </c>
       <c r="B907" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C907" s="3" t="s">
         <v>2199</v>
@@ -23255,7 +23273,7 @@
         <v>1615</v>
       </c>
       <c r="B908" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C908" s="3" t="s">
         <v>2201</v>
@@ -23271,14 +23289,14 @@
         <v>1615</v>
       </c>
       <c r="B909" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C909" s="3" t="s">
         <v>2203</v>
       </c>
       <c r="D909" s="3"/>
       <c r="E909" s="3"/>
-      <c r="P909" s="1" t="s">
+      <c r="P909" s="15" t="s">
         <v>2204</v>
       </c>
     </row>
@@ -23287,7 +23305,7 @@
         <v>1615</v>
       </c>
       <c r="B910" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C910" s="3" t="s">
         <v>2205</v>
@@ -23298,26 +23316,53 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="911" spans="1:5">
-      <c r="A911" s="3"/>
-      <c r="B911" s="3"/>
-      <c r="C911" s="3"/>
+    <row r="911" spans="1:16">
+      <c r="A911" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B911" s="3">
+        <v>15</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>2207</v>
+      </c>
       <c r="D911" s="3"/>
       <c r="E911" s="3"/>
-    </row>
-    <row r="912" spans="1:5">
-      <c r="A912" s="3"/>
-      <c r="B912" s="3"/>
-      <c r="C912" s="3"/>
+      <c r="P911" s="1" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="912" spans="1:16">
+      <c r="A912" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B912" s="3">
+        <v>16</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>2209</v>
+      </c>
       <c r="D912" s="3"/>
       <c r="E912" s="3"/>
-    </row>
-    <row r="913" spans="1:5">
-      <c r="A913" s="3"/>
-      <c r="B913" s="3"/>
-      <c r="C913" s="3"/>
+      <c r="P912" s="1" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="913" spans="1:16">
+      <c r="A913" s="3" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B913" s="3">
+        <v>17</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>2211</v>
+      </c>
       <c r="D913" s="3"/>
       <c r="E913" s="3"/>
+      <c r="P913" s="1" t="s">
+        <v>2212</v>
+      </c>
     </row>
     <row r="914" spans="1:5">
       <c r="A914" s="3"/>
@@ -23739,7 +23784,7 @@
       <c r="D973" s="3"/>
       <c r="E973" s="3"/>
     </row>
-    <row r="974" ht="44.25" customHeight="1" spans="1:5">
+    <row r="974" spans="1:5">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -23760,7 +23805,7 @@
       <c r="D976" s="3"/>
       <c r="E976" s="3"/>
     </row>
-    <row r="977" spans="1:5">
+    <row r="977" ht="44.25" customHeight="1" spans="1:5">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -24488,23 +24533,26 @@
       <c r="D1080" s="3"/>
       <c r="E1080" s="3"/>
     </row>
-    <row r="1081" spans="1:4">
+    <row r="1081" spans="1:5">
       <c r="A1081" s="3"/>
       <c r="B1081" s="3"/>
       <c r="C1081" s="3"/>
       <c r="D1081" s="3"/>
-    </row>
-    <row r="1082" spans="1:4">
+      <c r="E1081" s="3"/>
+    </row>
+    <row r="1082" spans="1:5">
       <c r="A1082" s="3"/>
       <c r="B1082" s="3"/>
       <c r="C1082" s="3"/>
       <c r="D1082" s="3"/>
-    </row>
-    <row r="1083" spans="1:4">
+      <c r="E1082" s="3"/>
+    </row>
+    <row r="1083" spans="1:5">
       <c r="A1083" s="3"/>
       <c r="B1083" s="3"/>
       <c r="C1083" s="3"/>
       <c r="D1083" s="3"/>
+      <c r="E1083" s="3"/>
     </row>
     <row r="1084" spans="1:4">
       <c r="A1084" s="3"/>
@@ -24559,6 +24607,24 @@
       <c r="B1092" s="3"/>
       <c r="C1092" s="3"/>
       <c r="D1092" s="3"/>
+    </row>
+    <row r="1093" spans="1:4">
+      <c r="A1093" s="3"/>
+      <c r="B1093" s="3"/>
+      <c r="C1093" s="3"/>
+      <c r="D1093" s="3"/>
+    </row>
+    <row r="1094" spans="1:4">
+      <c r="A1094" s="3"/>
+      <c r="B1094" s="3"/>
+      <c r="C1094" s="3"/>
+      <c r="D1094" s="3"/>
+    </row>
+    <row r="1095" spans="1:4">
+      <c r="A1095" s="3"/>
+      <c r="B1095" s="3"/>
+      <c r="C1095" s="3"/>
+      <c r="D1095" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Strings.xlsx
+++ b/Strings.xlsx
@@ -574,7 +574,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -583,7 +583,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="MS Gothic"/>
         <charset val="134"/>
@@ -592,7 +592,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -3471,7 +3471,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -3480,7 +3480,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="MS Gothic"/>
         <charset val="134"/>
@@ -3489,7 +3489,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -4490,7 +4490,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -4499,7 +4499,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="128"/>
@@ -4508,7 +4508,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -5086,7 +5086,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -5095,7 +5095,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="128"/>
@@ -5104,7 +5104,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -5113,7 +5113,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="128"/>
@@ -5122,7 +5122,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6498,7 +6498,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6507,7 +6507,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6516,7 +6516,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6525,7 +6525,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6536,7 +6536,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6545,7 +6545,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6554,7 +6554,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6563,7 +6563,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6577,7 +6577,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6586,7 +6586,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6595,7 +6595,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6604,7 +6604,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6615,7 +6615,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6624,7 +6624,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6633,7 +6633,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6642,7 +6642,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -6968,7 +6968,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -6977,7 +6977,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="128"/>
@@ -6986,7 +6986,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="等线"/>
         <charset val="134"/>
@@ -7350,7 +7350,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -7358,13 +7358,13 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -7376,23 +7376,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7555,13 +7549,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="MS Gothic"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -7870,28 +7864,31 @@
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -7900,124 +7897,121 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8037,7 +8031,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8046,14 +8040,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8386,7 +8383,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R1169"/>
-  <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="7.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="40.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.625" style="1" customWidth="1"/>
@@ -9845,14 +9842,14 @@
       <c r="B86" s="3">
         <v>17</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" s="15" t="s">
         <v>207</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>208</v>
       </c>
       <c r="E86" s="2"/>
-      <c r="P86" s="15" t="s">
+      <c r="P86" s="16" t="s">
         <v>209</v>
       </c>
     </row>
@@ -10498,7 +10495,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="124" ht="31" spans="1:16">
+    <row r="124" spans="1:16">
       <c r="A124" s="2" t="s">
         <v>236</v>
       </c>
@@ -10516,7 +10513,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="125" ht="31" spans="1:16">
+    <row r="125" spans="1:16">
       <c r="A125" s="2" t="s">
         <v>236</v>
       </c>
@@ -10822,7 +10819,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="142" ht="31" spans="1:16">
+    <row r="142" spans="1:16">
       <c r="A142" s="2" t="s">
         <v>236</v>
       </c>
@@ -23341,7 +23338,7 @@
       <c r="E891" s="2"/>
       <c r="P891" s="8"/>
     </row>
-    <row r="892" ht="31" spans="1:16">
+    <row r="892" ht="28" spans="1:16">
       <c r="A892" s="2" t="s">
         <v>2127</v>
       </c>
@@ -23359,7 +23356,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="893" ht="31" spans="1:16">
+    <row r="893" ht="28" spans="1:16">
       <c r="A893" s="2" t="s">
         <v>2127</v>
       </c>
@@ -23377,7 +23374,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="894" ht="31" spans="1:16">
+    <row r="894" ht="28" spans="1:16">
       <c r="A894" s="2" t="s">
         <v>2127</v>
       </c>
@@ -23395,7 +23392,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="895" ht="31" spans="1:16">
+    <row r="895" ht="28" spans="1:16">
       <c r="A895" s="2" t="s">
         <v>2127</v>
       </c>
@@ -23413,7 +23410,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="896" ht="31" spans="1:16">
+    <row r="896" ht="28" spans="1:16">
       <c r="A896" s="2" t="s">
         <v>2127</v>
       </c>
@@ -24061,7 +24058,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="934" ht="31" spans="1:16">
+    <row r="934" ht="28" spans="1:16">
       <c r="A934" s="2" t="s">
         <v>2227</v>
       </c>
@@ -24211,7 +24208,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="943" ht="108.5" spans="1:16">
+    <row r="943" ht="98" spans="1:16">
       <c r="A943" s="2" t="s">
         <v>2252</v>
       </c>
@@ -24227,7 +24224,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="944" ht="31" spans="1:16">
+    <row r="944" ht="28" spans="1:16">
       <c r="A944" s="2" t="s">
         <v>2252</v>
       </c>
@@ -24243,7 +24240,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="945" ht="124" spans="1:16">
+    <row r="945" ht="98" spans="1:16">
       <c r="A945" s="2" t="s">
         <v>2252</v>
       </c>
@@ -24760,7 +24757,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="979" ht="31" spans="1:16">
+    <row r="979" spans="1:16">
       <c r="A979" s="2" t="s">
         <v>1673</v>
       </c>
@@ -24792,7 +24789,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="981" ht="31" spans="1:16">
+    <row r="981" spans="1:16">
       <c r="A981" s="2" t="s">
         <v>1673</v>
       </c>
@@ -24836,7 +24833,7 @@
       </c>
       <c r="D983" s="2"/>
       <c r="E983" s="2"/>
-      <c r="P983" s="13" t="s">
+      <c r="P983" s="14" t="s">
         <v>2332</v>
       </c>
     </row>
@@ -24911,54 +24908,61 @@
       <c r="D988" s="2"/>
       <c r="E988" s="2"/>
     </row>
-    <row r="989" spans="1:5">
-      <c r="A989" s="2"/>
+    <row r="989" spans="1:16">
+      <c r="A989" s="13"/>
       <c r="B989" s="2"/>
-      <c r="C989" s="2"/>
+      <c r="C989" s="13"/>
       <c r="D989" s="2"/>
       <c r="E989" s="2"/>
-    </row>
-    <row r="990" spans="1:5">
-      <c r="A990" s="2"/>
+      <c r="P989" s="13"/>
+    </row>
+    <row r="990" spans="1:16">
+      <c r="A990" s="13"/>
       <c r="B990" s="2"/>
-      <c r="C990" s="2"/>
+      <c r="C990" s="13"/>
       <c r="D990" s="2"/>
       <c r="E990" s="2"/>
-    </row>
-    <row r="991" spans="1:5">
-      <c r="A991" s="2"/>
+      <c r="P990" s="13"/>
+    </row>
+    <row r="991" spans="1:16">
+      <c r="A991" s="13"/>
       <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
+      <c r="C991" s="13"/>
       <c r="D991" s="2"/>
       <c r="E991" s="2"/>
-    </row>
-    <row r="992" spans="1:5">
-      <c r="A992" s="2"/>
+      <c r="P991" s="13"/>
+    </row>
+    <row r="992" spans="1:16">
+      <c r="A992" s="13"/>
       <c r="B992" s="2"/>
-      <c r="C992" s="2"/>
+      <c r="C992" s="13"/>
       <c r="D992" s="2"/>
       <c r="E992" s="2"/>
-    </row>
-    <row r="993" spans="1:5">
-      <c r="A993" s="2"/>
+      <c r="P992" s="13"/>
+    </row>
+    <row r="993" spans="1:16">
+      <c r="A993" s="13"/>
       <c r="B993" s="2"/>
-      <c r="C993" s="2"/>
+      <c r="C993" s="13"/>
       <c r="D993" s="2"/>
       <c r="E993" s="2"/>
-    </row>
-    <row r="994" spans="1:5">
-      <c r="A994" s="2"/>
+      <c r="P993" s="13"/>
+    </row>
+    <row r="994" spans="1:16">
+      <c r="A994" s="13"/>
       <c r="B994" s="2"/>
-      <c r="C994" s="2"/>
+      <c r="C994" s="13"/>
       <c r="D994" s="2"/>
       <c r="E994" s="2"/>
-    </row>
-    <row r="995" spans="1:5">
-      <c r="A995" s="2"/>
+      <c r="P994" s="13"/>
+    </row>
+    <row r="995" spans="1:16">
+      <c r="A995" s="13"/>
       <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
+      <c r="C995" s="13"/>
       <c r="D995" s="2"/>
       <c r="E995" s="2"/>
+      <c r="P995" s="13"/>
     </row>
     <row r="996" spans="1:5">
       <c r="A996" s="2"/>
